--- a/光伏配储项目/电价数据/2026/邹鲁站.xlsx
+++ b/光伏配储项目/电价数据/2026/邹鲁站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33033</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.70172</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07539</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7516</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.6424</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17314</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.63897</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6246900000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60225</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.22401</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6908099999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.91313</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.57972</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.33683</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.65461</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.06029</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.06091</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.4164</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.37664</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45865</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.73234</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.79867</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.54773</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.76335</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.78692</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.78991</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.70492</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.39563</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.66306</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.20105</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.85472</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.71281</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6855599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50688</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.55543</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.55148</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66771</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.62888</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.93186</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.85358</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.77288</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.73861</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.73737</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.72662</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.34835</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.49396</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.28349</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.4715</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0765</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.45614</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.37604</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.32356</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.2341</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20015</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.99017</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.37933</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.13007</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.48814</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.99778</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.89485</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33139</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.16772</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20475</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.12771</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.92861</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.75009</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7381</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.09678</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.09472</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1.16199</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.09437</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78539</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.79822</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.81643</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.1023</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.6117999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6911799999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.15727</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.08812</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.78307</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.88188</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.57504</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.22137</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.61713</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45798</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51391</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.57557</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.9162899999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.98337</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7935399999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.72288</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.69852</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70239</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5258200000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.56292</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6779700000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.91895</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81235</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.58892</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48741</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.68623</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50301</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.73627</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03215</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.2603</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8070900000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.44094</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8825499999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58012</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7248300000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.46433</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3387</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5581199999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.8978200000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46451</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.49065</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.8847200000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.66246</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.5065299999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.68772</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.0084</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.53633</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8862100000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.79262</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.55979</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5997100000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.70225</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9669099999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6322000000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66375</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6722100000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.64535</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.55248</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.51788</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.50556</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.49087</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.41405</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14337</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10612</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31696</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.27566</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.20024</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24759</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21395</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24846</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20013</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19386</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00928</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31562</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.48441</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.47855</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78922</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65339</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5720599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46667</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59504</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6409600000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9621799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.58688</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.80031</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.03602</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.8191799999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6625700000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17806</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32324</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.81016</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.48732</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.65783</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.54035</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23543</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.58527</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.61295</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.45778</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.50676</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.69755</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.55808</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.51625</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5581699999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.51407</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.57759</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.32581</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.2704</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.80365</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.89283</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.56792</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.80777</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.59299</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.50108</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.48472</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.17406</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.48787</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.44909</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32438</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.21998</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18575</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18299</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.18263</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18531</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.18942</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23371</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26298</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2806</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43595</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30315</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.03976</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6446900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48993</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54311</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7879400000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6143</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.49638</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.53142</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.42295</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.50503</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.48166</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.5787599999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5459400000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.54067</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70205</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46593</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.4894</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30443</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19741</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18971</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27391</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18886</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18859</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16522</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25373</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3208</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.01974</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5821000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5156799999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20324</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29629</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49651</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6106900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5739299999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.76135</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31385</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42203</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5758300000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6546000000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71026</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48389</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.48632</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6764600000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.55248</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64228</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31467</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.00588</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.5071</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5324800000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.56245</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.52727</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.50451</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.53123</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34948</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23224</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23303</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16492</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.007480000000000001</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.27242</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01026</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.009730000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16516</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02137</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16396</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01025</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15465</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19442</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1568</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15948</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16217</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01077</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16485</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01088</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.03627</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17563</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.61856</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21772</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26968</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.22414</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.21762</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.24098</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33628</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22776</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03775</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18295</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18001</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02023</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19992</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03204</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01798</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01799</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01813</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03228</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01831</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17313</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03204</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03203</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01727</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01644</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24393</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02316</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00775</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00075</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02024</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.06815</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02821</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01739</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2677</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16098</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16529</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16271</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15884</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14792</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01303</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.00915</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18935</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04419</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23278</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85721</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86226</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09024</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01745</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.52725</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00177</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.63098</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7385</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.86824</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57331</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.72162</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7412000000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7394299999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7429199999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30644</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26773</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18721</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21279</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25328</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19503</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15829</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16094</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15366</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17823</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22888</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23828</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24737</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25112</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2902</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54653</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20447</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7464</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75764</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.51378</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.78565</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31556</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49083</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.00878</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.76355</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5344800000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.68071</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55079</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6548200000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.61485</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.94594</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6580900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55552</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32017</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51885</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.54834</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.7352799999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.74815</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.7502799999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.58745</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5373600000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3241</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.66115</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.95496</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.9916699999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.60329</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.7697999999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.07593</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.64216</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7058099999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33767</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17611</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19867</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14655</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04788000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14353</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18771</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22686</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.20759</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.24475</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.49503</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.48422</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.9329700000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.06341</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.67523</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.75154</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.85776</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.48667</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5515800000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.92904</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.79747</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.01334</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.58443</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.07142</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.48314</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.9651799999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.48864</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.91174</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.95662</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.72993</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.49221</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36765</v>
       </c>
     </row>
   </sheetData>
